--- a/data/inventories_ei310_monte_carlo.xlsx
+++ b/data/inventories_ei310_monte_carlo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Propanol production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD671230-D5EF-4ED3-BEF5-A2FDC21020E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69CBE66-46BF-449F-B976-1863927EFD06}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="5" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
@@ -8947,7 +8947,7 @@
         <v>183</v>
       </c>
       <c r="C24" s="11">
-        <v>6.1986160194061453E-2</v>
+        <v>1.1909130920840772E-2</v>
       </c>
       <c r="D24" s="35" t="s">
         <v>7</v>
@@ -8970,7 +8970,7 @@
         <v>235</v>
       </c>
       <c r="C25" s="11">
-        <v>1.0096843754568836</v>
+        <v>4.3154720378960579E-2</v>
       </c>
       <c r="D25" s="35" t="s">
         <v>7</v>
@@ -8992,8 +8992,9 @@
       <c r="B26" t="s">
         <v>164</v>
       </c>
-      <c r="C26" s="32">
-        <v>-1.373048181564959E-3</v>
+      <c r="C26" s="21">
+        <f>-0.354990105418442/1000</f>
+        <v>-3.54990105418442E-4</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -9408,7 +9409,7 @@
         <v>183</v>
       </c>
       <c r="C48" s="11">
-        <v>6.1986160194061453E-2</v>
+        <v>1.1909130920840772E-2</v>
       </c>
       <c r="D48" s="35" t="s">
         <v>7</v>
@@ -9431,7 +9432,7 @@
         <v>235</v>
       </c>
       <c r="C49" s="11">
-        <v>1.0096843754568836</v>
+        <v>4.3154720378960579E-2</v>
       </c>
       <c r="D49" s="35" t="s">
         <v>7</v>
@@ -9453,8 +9454,9 @@
       <c r="B50" t="s">
         <v>164</v>
       </c>
-      <c r="C50" s="32">
-        <v>-1.373048181564959E-3</v>
+      <c r="C50" s="21">
+        <f>-0.354990105418442/1000</f>
+        <v>-3.54990105418442E-4</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -9894,7 +9896,7 @@
         <v>183</v>
       </c>
       <c r="C73" s="11">
-        <v>8.2415447123467735E-3</v>
+        <v>5.247713160436659E-4</v>
       </c>
       <c r="D73" s="35" t="s">
         <v>7</v>
@@ -9917,7 +9919,7 @@
         <v>235</v>
       </c>
       <c r="C74" s="11">
-        <v>0.14033639148759799</v>
+        <v>4.0309778724925641E-3</v>
       </c>
       <c r="D74" s="35" t="s">
         <v>7</v>
@@ -9940,7 +9942,8 @@
         <v>164</v>
       </c>
       <c r="C75" s="21">
-        <v>-1.5016213007088301E-4</v>
+        <f>-0.00590234822670513/1000</f>
+        <v>-5.90234822670513E-6</v>
       </c>
       <c r="D75" t="s">
         <v>17</v>
@@ -10380,7 +10383,7 @@
         <v>183</v>
       </c>
       <c r="C98" s="11">
-        <v>8.2415447123467735E-3</v>
+        <v>5.247713160436659E-4</v>
       </c>
       <c r="D98" s="35" t="s">
         <v>7</v>
@@ -10403,7 +10406,7 @@
         <v>235</v>
       </c>
       <c r="C99" s="11">
-        <v>0.14033639148759799</v>
+        <v>4.0309778724925641E-3</v>
       </c>
       <c r="D99" s="35" t="s">
         <v>7</v>
@@ -10426,7 +10429,8 @@
         <v>164</v>
       </c>
       <c r="C100" s="21">
-        <v>-1.5016213007088301E-4</v>
+        <f>-0.00590234822670513/1000</f>
+        <v>-5.90234822670513E-6</v>
       </c>
       <c r="D100" t="s">
         <v>17</v>
